--- a/Results/Study 1/AlexNet/Confusion Matrices.xlsx
+++ b/Results/Study 1/AlexNet/Confusion Matrices.xlsx
@@ -400,10 +400,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>369</v>
+        <v>452</v>
       </c>
       <c r="C2">
-        <v>271</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -411,10 +411,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>266</v>
+        <v>355</v>
       </c>
       <c r="C3">
-        <v>374</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -440,10 +440,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="C2">
-        <v>61</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -451,10 +451,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C3">
-        <v>85</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
